--- a/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-Evenement.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
